--- a/chuangdi/数据/规格单价表-演示.xlsx
+++ b/chuangdi/数据/规格单价表-演示.xlsx
@@ -973,7 +973,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="37" fillId="37" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="37" fillId="37" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -985,22 +985,22 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="37" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2100,7 +2100,7 @@
       <c r="A5" s="44" t="n">
         <v>10.416</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>贴片</t>
         </is>
@@ -2131,7 +2131,7 @@
       <c r="A6" s="44" t="n">
         <v>10.416</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>直插</t>
         </is>
@@ -2283,130 +2283,202 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="43" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="50">
-        <f>IF(C11="","",E11+F11*G11+H11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="7" t="n"/>
+      <c r="A11" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>贴片</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D11" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G11" s="48">
+        <f>IF(A11="","",C11+D11*E11+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="41" t="inlineStr">
+        <is>
+          <t>演示价·套件</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="43" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
-      <c r="G12" s="50">
-        <f>IF(C12="","",E12+F12*G12+H12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="7" t="n"/>
+      <c r="A12" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>贴片</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G12" s="48">
+        <f>IF(A12="","",C12+D12*E12+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="41" t="inlineStr">
+        <is>
+          <t>演示价·套件</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="50">
-        <f>IF(C13="","",E13+F13*G13+H13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="7" t="n"/>
+      <c r="A13" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>贴片</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F13" s="45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G13" s="48">
+        <f>IF(A13="","",C13+D13*E13+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="41" t="inlineStr">
+        <is>
+          <t>演示价·套件</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
-      <c r="G14" s="50">
-        <f>IF(C14="","",E14+F14*G14+H14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="7" t="n"/>
+      <c r="A14" s="44" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>贴片</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="48">
+        <f>IF(A14="","",C14+D14*E14+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="inlineStr">
+        <is>
+          <t>演示价·套件</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="n"/>
+      <c r="A15" s="49" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="43" t="n"/>
-      <c r="D15" s="49" t="n"/>
+      <c r="D15" s="50" t="n"/>
       <c r="E15" s="43" t="n"/>
       <c r="F15" s="43" t="n"/>
-      <c r="G15" s="50">
+      <c r="G15" s="48">
         <f>IF(C15="","",E15+F15*G15+H15)</f>
         <v/>
       </c>
       <c r="H15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="n"/>
+      <c r="A16" s="49" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="43" t="n"/>
-      <c r="D16" s="49" t="n"/>
+      <c r="D16" s="50" t="n"/>
       <c r="E16" s="43" t="n"/>
       <c r="F16" s="43" t="n"/>
-      <c r="G16" s="50">
+      <c r="G16" s="48">
         <f>IF(C16="","",E16+F16*G16+H16)</f>
         <v/>
       </c>
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="n"/>
+      <c r="A17" s="49" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="43" t="n"/>
-      <c r="D17" s="49" t="n"/>
+      <c r="D17" s="50" t="n"/>
       <c r="E17" s="43" t="n"/>
       <c r="F17" s="43" t="n"/>
-      <c r="G17" s="50">
+      <c r="G17" s="48">
         <f>IF(C17="","",E17+F17*G17+H17)</f>
         <v/>
       </c>
       <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="n"/>
+      <c r="A18" s="49" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="43" t="n"/>
-      <c r="D18" s="49" t="n"/>
+      <c r="D18" s="50" t="n"/>
       <c r="E18" s="43" t="n"/>
       <c r="F18" s="43" t="n"/>
-      <c r="G18" s="50">
+      <c r="G18" s="48">
         <f>IF(C18="","",E18+F18*G18+H18)</f>
         <v/>
       </c>
       <c r="H18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="n"/>
+      <c r="A19" s="49" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="43" t="n"/>
-      <c r="D19" s="49" t="n"/>
+      <c r="D19" s="50" t="n"/>
       <c r="E19" s="43" t="n"/>
       <c r="F19" s="43" t="n"/>
-      <c r="G19" s="50">
+      <c r="G19" s="48">
         <f>IF(C19="","",E19+F19*G19+H19)</f>
         <v/>
       </c>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="n"/>
+      <c r="A20" s="49" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="43" t="n"/>
-      <c r="D20" s="49" t="n"/>
+      <c r="D20" s="50" t="n"/>
       <c r="E20" s="43" t="n"/>
       <c r="F20" s="43" t="n"/>
-      <c r="G20" s="50">
+      <c r="G20" s="48">
         <f>IF(C20="","",E20+F20*G20+H20)</f>
         <v/>
       </c>
@@ -2599,7 +2671,7 @@
           <t>P33.33</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="51" t="n">
         <v>33.33</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2644,41 +2716,41 @@
       <c r="L5" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="M5" s="51" t="n">
+      <c r="M5" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N5" s="51" t="n"/>
-      <c r="O5" s="52">
+      <c r="N5" s="52" t="n"/>
+      <c r="O5" s="53">
         <f>IF(J5="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J5))</f>
         <v/>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="53">
         <f>IF(J5="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J5))</f>
         <v/>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="53">
         <f>IF(J5="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J5))</f>
         <v/>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="53">
         <f>IF(B5="","",L5*O5+M5*P5+N5*Q5)</f>
         <v/>
       </c>
-      <c r="S5" s="53" t="n">
+      <c r="S5" s="44" t="n">
         <v>60</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="53">
         <f>IF(B5="","",SUMIFS(套件单价!G:G,套件单价!A:A,B5,套件单价!B:B,K5))</f>
         <v/>
       </c>
-      <c r="U5" s="44" t="n">
+      <c r="U5" s="51" t="n">
         <v>1.5</v>
       </c>
-      <c r="V5" s="52">
+      <c r="V5" s="53">
         <f>IF(B5="","",R5+S5+T5)</f>
         <v/>
       </c>
-      <c r="W5" s="52">
+      <c r="W5" s="53">
         <f>IF(B5="","",V5+U5)</f>
         <v/>
       </c>
@@ -2694,7 +2766,7 @@
           <t>P33.33</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="51" t="n">
         <v>33.33</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2739,43 +2811,43 @@
       <c r="L6" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="M6" s="51" t="n">
+      <c r="M6" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N6" s="51" t="n">
+      <c r="N6" s="52" t="n">
         <v>32</v>
       </c>
-      <c r="O6" s="52">
+      <c r="O6" s="53">
         <f>IF(J6="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J6))</f>
         <v/>
       </c>
-      <c r="P6" s="52">
+      <c r="P6" s="53">
         <f>IF(J6="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J6))</f>
         <v/>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="53">
         <f>IF(J6="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J6))</f>
         <v/>
       </c>
-      <c r="R6" s="52">
+      <c r="R6" s="53">
         <f>IF(B6="","",L6*O6+M6*P6+N6*Q6)</f>
         <v/>
       </c>
-      <c r="S6" s="53" t="n">
+      <c r="S6" s="44" t="n">
         <v>66</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="53">
         <f>IF(B6="","",SUMIFS(套件单价!G:G,套件单价!A:A,B6,套件单价!B:B,K6))</f>
         <v/>
       </c>
-      <c r="U6" s="44" t="n">
+      <c r="U6" s="51" t="n">
         <v>1.5</v>
       </c>
-      <c r="V6" s="52">
+      <c r="V6" s="53">
         <f>IF(B6="","",R6+S6+T6)</f>
         <v/>
       </c>
-      <c r="W6" s="52">
+      <c r="W6" s="53">
         <f>IF(B6="","",V6+U6)</f>
         <v/>
       </c>
@@ -2792,7 +2864,7 @@
           <t>P33.33</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="51" t="n">
         <v>33.33</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2837,41 +2909,41 @@
       <c r="L7" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="M7" s="51" t="n">
+      <c r="M7" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N7" s="51" t="n"/>
-      <c r="O7" s="52">
+      <c r="N7" s="52" t="n"/>
+      <c r="O7" s="53">
         <f>IF(J7="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J7))</f>
         <v/>
       </c>
-      <c r="P7" s="52">
+      <c r="P7" s="53">
         <f>IF(J7="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J7))</f>
         <v/>
       </c>
-      <c r="Q7" s="52">
+      <c r="Q7" s="53">
         <f>IF(J7="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J7))</f>
         <v/>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="53">
         <f>IF(B7="","",L7*O7+M7*P7+N7*Q7)</f>
         <v/>
       </c>
-      <c r="S7" s="53" t="n">
+      <c r="S7" s="44" t="n">
         <v>60</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="53">
         <f>IF(B7="","",SUMIFS(套件单价!G:G,套件单价!A:A,B7,套件单价!B:B,K7))</f>
         <v/>
       </c>
-      <c r="U7" s="44" t="n">
+      <c r="U7" s="51" t="n">
         <v>1.5</v>
       </c>
-      <c r="V7" s="52">
+      <c r="V7" s="53">
         <f>IF(B7="","",R7+S7+T7)</f>
         <v/>
       </c>
-      <c r="W7" s="52">
+      <c r="W7" s="53">
         <f>IF(B7="","",V7+U7)</f>
         <v/>
       </c>
@@ -2888,7 +2960,7 @@
           <t>P33.33</t>
         </is>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="51" t="n">
         <v>33.33</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2933,41 +3005,41 @@
       <c r="L8" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="M8" s="51" t="n">
+      <c r="M8" s="52" t="n">
         <v>32</v>
       </c>
-      <c r="N8" s="51" t="n"/>
-      <c r="O8" s="52">
+      <c r="N8" s="52" t="n"/>
+      <c r="O8" s="53">
         <f>IF(J8="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J8))</f>
         <v/>
       </c>
-      <c r="P8" s="52">
+      <c r="P8" s="53">
         <f>IF(J8="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J8))</f>
         <v/>
       </c>
-      <c r="Q8" s="52">
+      <c r="Q8" s="53">
         <f>IF(J8="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J8))</f>
         <v/>
       </c>
-      <c r="R8" s="52">
+      <c r="R8" s="53">
         <f>IF(B8="","",L8*O8+M8*P8+N8*Q8)</f>
         <v/>
       </c>
-      <c r="S8" s="53" t="n">
+      <c r="S8" s="44" t="n">
         <v>60</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="53">
         <f>IF(B8="","",SUMIFS(套件单价!G:G,套件单价!A:A,B8,套件单价!B:B,K8))</f>
         <v/>
       </c>
-      <c r="U8" s="44" t="n">
+      <c r="U8" s="51" t="n">
         <v>1.5</v>
       </c>
-      <c r="V8" s="52">
+      <c r="V8" s="53">
         <f>IF(B8="","",R8+S8+T8)</f>
         <v/>
       </c>
-      <c r="W8" s="52">
+      <c r="W8" s="53">
         <f>IF(B8="","",V8+U8)</f>
         <v/>
       </c>
@@ -2984,7 +3056,7 @@
           <t>P31.25</t>
         </is>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="51" t="n">
         <v>31.25</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3029,41 +3101,41 @@
       <c r="L9" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="M9" s="51" t="n">
+      <c r="M9" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N9" s="51" t="n"/>
-      <c r="O9" s="52">
+      <c r="N9" s="52" t="n"/>
+      <c r="O9" s="53">
         <f>IF(J9="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J9))</f>
         <v/>
       </c>
-      <c r="P9" s="52">
+      <c r="P9" s="53">
         <f>IF(J9="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J9))</f>
         <v/>
       </c>
-      <c r="Q9" s="52">
+      <c r="Q9" s="53">
         <f>IF(J9="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J9))</f>
         <v/>
       </c>
-      <c r="R9" s="52">
+      <c r="R9" s="53">
         <f>IF(B9="","",L9*O9+M9*P9+N9*Q9)</f>
         <v/>
       </c>
-      <c r="S9" s="53" t="n">
+      <c r="S9" s="44" t="n">
         <v>63.85</v>
       </c>
-      <c r="T9" s="52">
+      <c r="T9" s="53">
         <f>IF(B9="","",SUMIFS(套件单价!G:G,套件单价!A:A,B9,套件单价!B:B,K9))</f>
         <v/>
       </c>
-      <c r="U9" s="44" t="n">
+      <c r="U9" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="V9" s="52">
+      <c r="V9" s="53">
         <f>IF(B9="","",R9+S9+T9)</f>
         <v/>
       </c>
-      <c r="W9" s="52">
+      <c r="W9" s="53">
         <f>IF(B9="","",V9+U9)</f>
         <v/>
       </c>
@@ -3080,7 +3152,7 @@
           <t>P31.25</t>
         </is>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="51" t="n">
         <v>31.25</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3125,43 +3197,43 @@
       <c r="L10" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="M10" s="51" t="n">
+      <c r="M10" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N10" s="51" t="n">
+      <c r="N10" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="O10" s="52">
+      <c r="O10" s="53">
         <f>IF(J10="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J10))</f>
         <v/>
       </c>
-      <c r="P10" s="52">
+      <c r="P10" s="53">
         <f>IF(J10="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J10))</f>
         <v/>
       </c>
-      <c r="Q10" s="52">
+      <c r="Q10" s="53">
         <f>IF(J10="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J10))</f>
         <v/>
       </c>
-      <c r="R10" s="52">
+      <c r="R10" s="53">
         <f>IF(B10="","",L10*O10+M10*P10+N10*Q10)</f>
         <v/>
       </c>
-      <c r="S10" s="53" t="n">
+      <c r="S10" s="44" t="n">
         <v>69.84999999999999</v>
       </c>
-      <c r="T10" s="52">
+      <c r="T10" s="53">
         <f>IF(B10="","",SUMIFS(套件单价!G:G,套件单价!A:A,B10,套件单价!B:B,K10))</f>
         <v/>
       </c>
-      <c r="U10" s="44" t="n">
+      <c r="U10" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="V10" s="52">
+      <c r="V10" s="53">
         <f>IF(B10="","",R10+S10+T10)</f>
         <v/>
       </c>
-      <c r="W10" s="52">
+      <c r="W10" s="53">
         <f>IF(B10="","",V10+U10)</f>
         <v/>
       </c>
@@ -3178,7 +3250,7 @@
           <t>P31.25</t>
         </is>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B11" s="51" t="n">
         <v>31.25</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3223,41 +3295,41 @@
       <c r="L11" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="M11" s="51" t="n">
+      <c r="M11" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N11" s="51" t="n"/>
-      <c r="O11" s="52">
+      <c r="N11" s="52" t="n"/>
+      <c r="O11" s="53">
         <f>IF(J11="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J11))</f>
         <v/>
       </c>
-      <c r="P11" s="52">
+      <c r="P11" s="53">
         <f>IF(J11="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J11))</f>
         <v/>
       </c>
-      <c r="Q11" s="52">
+      <c r="Q11" s="53">
         <f>IF(J11="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J11))</f>
         <v/>
       </c>
-      <c r="R11" s="52">
+      <c r="R11" s="53">
         <f>IF(B11="","",L11*O11+M11*P11+N11*Q11)</f>
         <v/>
       </c>
-      <c r="S11" s="53" t="n">
+      <c r="S11" s="44" t="n">
         <v>63.85</v>
       </c>
-      <c r="T11" s="52">
+      <c r="T11" s="53">
         <f>IF(B11="","",SUMIFS(套件单价!G:G,套件单价!A:A,B11,套件单价!B:B,K11))</f>
         <v/>
       </c>
-      <c r="U11" s="44" t="n">
+      <c r="U11" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="V11" s="52">
+      <c r="V11" s="53">
         <f>IF(B11="","",R11+S11+T11)</f>
         <v/>
       </c>
-      <c r="W11" s="52">
+      <c r="W11" s="53">
         <f>IF(B11="","",V11+U11)</f>
         <v/>
       </c>
@@ -3274,7 +3346,7 @@
           <t>P31.25</t>
         </is>
       </c>
-      <c r="B12" s="44" t="n">
+      <c r="B12" s="51" t="n">
         <v>31.25</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3319,43 +3391,43 @@
       <c r="L12" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="M12" s="51" t="n">
+      <c r="M12" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N12" s="51" t="n">
+      <c r="N12" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12" s="53">
         <f>IF(J12="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J12))</f>
         <v/>
       </c>
-      <c r="P12" s="52">
+      <c r="P12" s="53">
         <f>IF(J12="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J12))</f>
         <v/>
       </c>
-      <c r="Q12" s="52">
+      <c r="Q12" s="53">
         <f>IF(J12="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J12))</f>
         <v/>
       </c>
-      <c r="R12" s="52">
+      <c r="R12" s="53">
         <f>IF(B12="","",L12*O12+M12*P12+N12*Q12)</f>
         <v/>
       </c>
-      <c r="S12" s="53" t="n">
+      <c r="S12" s="44" t="n">
         <v>69.84999999999999</v>
       </c>
-      <c r="T12" s="52">
+      <c r="T12" s="53">
         <f>IF(B12="","",SUMIFS(套件单价!G:G,套件单价!A:A,B12,套件单价!B:B,K12))</f>
         <v/>
       </c>
-      <c r="U12" s="44" t="n">
+      <c r="U12" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="V12" s="52">
+      <c r="V12" s="53">
         <f>IF(B12="","",R12+S12+T12)</f>
         <v/>
       </c>
-      <c r="W12" s="52">
+      <c r="W12" s="53">
         <f>IF(B12="","",V12+U12)</f>
         <v/>
       </c>
@@ -3372,7 +3444,7 @@
           <t>P31.25</t>
         </is>
       </c>
-      <c r="B13" s="44" t="n">
+      <c r="B13" s="51" t="n">
         <v>31.25</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3417,41 +3489,41 @@
       <c r="L13" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="M13" s="51" t="n">
+      <c r="M13" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N13" s="51" t="n"/>
-      <c r="O13" s="52">
+      <c r="N13" s="52" t="n"/>
+      <c r="O13" s="53">
         <f>IF(J13="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J13))</f>
         <v/>
       </c>
-      <c r="P13" s="52">
+      <c r="P13" s="53">
         <f>IF(J13="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J13))</f>
         <v/>
       </c>
-      <c r="Q13" s="52">
+      <c r="Q13" s="53">
         <f>IF(J13="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J13))</f>
         <v/>
       </c>
-      <c r="R13" s="52">
+      <c r="R13" s="53">
         <f>IF(B13="","",L13*O13+M13*P13+N13*Q13)</f>
         <v/>
       </c>
-      <c r="S13" s="53" t="n">
+      <c r="S13" s="44" t="n">
         <v>63.85</v>
       </c>
-      <c r="T13" s="52">
+      <c r="T13" s="53">
         <f>IF(B13="","",SUMIFS(套件单价!G:G,套件单价!A:A,B13,套件单价!B:B,K13))</f>
         <v/>
       </c>
-      <c r="U13" s="44" t="n">
+      <c r="U13" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="V13" s="52">
+      <c r="V13" s="53">
         <f>IF(B13="","",R13+S13+T13)</f>
         <v/>
       </c>
-      <c r="W13" s="52">
+      <c r="W13" s="53">
         <f>IF(B13="","",V13+U13)</f>
         <v/>
       </c>
@@ -3468,7 +3540,7 @@
           <t>P31.25</t>
         </is>
       </c>
-      <c r="B14" s="44" t="n">
+      <c r="B14" s="51" t="n">
         <v>31.25</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3513,43 +3585,43 @@
       <c r="L14" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="M14" s="51" t="n">
+      <c r="M14" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N14" s="51" t="n">
+      <c r="N14" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="O14" s="52">
+      <c r="O14" s="53">
         <f>IF(J14="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J14))</f>
         <v/>
       </c>
-      <c r="P14" s="52">
+      <c r="P14" s="53">
         <f>IF(J14="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J14))</f>
         <v/>
       </c>
-      <c r="Q14" s="52">
+      <c r="Q14" s="53">
         <f>IF(J14="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J14))</f>
         <v/>
       </c>
-      <c r="R14" s="52">
+      <c r="R14" s="53">
         <f>IF(B14="","",L14*O14+M14*P14+N14*Q14)</f>
         <v/>
       </c>
-      <c r="S14" s="53" t="n">
+      <c r="S14" s="44" t="n">
         <v>69.84999999999999</v>
       </c>
-      <c r="T14" s="52">
+      <c r="T14" s="53">
         <f>IF(B14="","",SUMIFS(套件单价!G:G,套件单价!A:A,B14,套件单价!B:B,K14))</f>
         <v/>
       </c>
-      <c r="U14" s="44" t="n">
+      <c r="U14" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="V14" s="52">
+      <c r="V14" s="53">
         <f>IF(B14="","",R14+S14+T14)</f>
         <v/>
       </c>
-      <c r="W14" s="52">
+      <c r="W14" s="53">
         <f>IF(B14="","",V14+U14)</f>
         <v/>
       </c>
@@ -3566,7 +3638,7 @@
           <t>P25</t>
         </is>
       </c>
-      <c r="B15" s="44" t="n">
+      <c r="B15" s="51" t="n">
         <v>25</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3611,41 +3683,41 @@
       <c r="L15" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="M15" s="51" t="n">
+      <c r="M15" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N15" s="51" t="n"/>
-      <c r="O15" s="52">
+      <c r="N15" s="52" t="n"/>
+      <c r="O15" s="53">
         <f>IF(J15="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J15))</f>
         <v/>
       </c>
-      <c r="P15" s="52">
+      <c r="P15" s="53">
         <f>IF(J15="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J15))</f>
         <v/>
       </c>
-      <c r="Q15" s="52">
+      <c r="Q15" s="53">
         <f>IF(J15="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J15))</f>
         <v/>
       </c>
-      <c r="R15" s="52">
+      <c r="R15" s="53">
         <f>IF(B15="","",L15*O15+M15*P15+N15*Q15)</f>
         <v/>
       </c>
-      <c r="S15" s="53" t="n">
+      <c r="S15" s="44" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="T15" s="52">
+      <c r="T15" s="53">
         <f>IF(B15="","",SUMIFS(套件单价!G:G,套件单价!A:A,B15,套件单价!B:B,K15))</f>
         <v/>
       </c>
-      <c r="U15" s="44" t="n">
+      <c r="U15" s="51" t="n">
         <v>2.5</v>
       </c>
-      <c r="V15" s="52">
+      <c r="V15" s="53">
         <f>IF(B15="","",R15+S15+T15)</f>
         <v/>
       </c>
-      <c r="W15" s="52">
+      <c r="W15" s="53">
         <f>IF(B15="","",V15+U15)</f>
         <v/>
       </c>
@@ -3662,7 +3734,7 @@
           <t>P25</t>
         </is>
       </c>
-      <c r="B16" s="44" t="n">
+      <c r="B16" s="51" t="n">
         <v>25</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3707,41 +3779,41 @@
       <c r="L16" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="M16" s="51" t="n">
+      <c r="M16" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N16" s="51" t="n"/>
-      <c r="O16" s="52">
+      <c r="N16" s="52" t="n"/>
+      <c r="O16" s="53">
         <f>IF(J16="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J16))</f>
         <v/>
       </c>
-      <c r="P16" s="52">
+      <c r="P16" s="53">
         <f>IF(J16="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J16))</f>
         <v/>
       </c>
-      <c r="Q16" s="52">
+      <c r="Q16" s="53">
         <f>IF(J16="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J16))</f>
         <v/>
       </c>
-      <c r="R16" s="52">
+      <c r="R16" s="53">
         <f>IF(B16="","",L16*O16+M16*P16+N16*Q16)</f>
         <v/>
       </c>
-      <c r="S16" s="53" t="n">
+      <c r="S16" s="44" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="T16" s="52">
+      <c r="T16" s="53">
         <f>IF(B16="","",SUMIFS(套件单价!G:G,套件单价!A:A,B16,套件单价!B:B,K16))</f>
         <v/>
       </c>
-      <c r="U16" s="44" t="n">
+      <c r="U16" s="51" t="n">
         <v>2.5</v>
       </c>
-      <c r="V16" s="52">
+      <c r="V16" s="53">
         <f>IF(B16="","",R16+S16+T16)</f>
         <v/>
       </c>
-      <c r="W16" s="52">
+      <c r="W16" s="53">
         <f>IF(B16="","",V16+U16)</f>
         <v/>
       </c>
@@ -3758,7 +3830,7 @@
           <t>P25</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="51" t="n">
         <v>25</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3803,43 +3875,43 @@
       <c r="L17" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="M17" s="51" t="n">
+      <c r="M17" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N17" s="51" t="n">
+      <c r="N17" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="O17" s="52">
+      <c r="O17" s="53">
         <f>IF(J17="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J17))</f>
         <v/>
       </c>
-      <c r="P17" s="52">
+      <c r="P17" s="53">
         <f>IF(J17="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J17))</f>
         <v/>
       </c>
-      <c r="Q17" s="52">
+      <c r="Q17" s="53">
         <f>IF(J17="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J17))</f>
         <v/>
       </c>
-      <c r="R17" s="52">
+      <c r="R17" s="53">
         <f>IF(B17="","",L17*O17+M17*P17+N17*Q17)</f>
         <v/>
       </c>
-      <c r="S17" s="53" t="n">
+      <c r="S17" s="44" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="T17" s="52">
+      <c r="T17" s="53">
         <f>IF(B17="","",SUMIFS(套件单价!G:G,套件单价!A:A,B17,套件单价!B:B,K17))</f>
         <v/>
       </c>
-      <c r="U17" s="44" t="n">
+      <c r="U17" s="51" t="n">
         <v>2.5</v>
       </c>
-      <c r="V17" s="52">
+      <c r="V17" s="53">
         <f>IF(B17="","",R17+S17+T17)</f>
         <v/>
       </c>
-      <c r="W17" s="52">
+      <c r="W17" s="53">
         <f>IF(B17="","",V17+U17)</f>
         <v/>
       </c>
@@ -3856,7 +3928,7 @@
           <t>P25</t>
         </is>
       </c>
-      <c r="B18" s="44" t="n">
+      <c r="B18" s="51" t="n">
         <v>25</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3901,41 +3973,41 @@
       <c r="L18" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="M18" s="51" t="n">
+      <c r="M18" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N18" s="51" t="n"/>
-      <c r="O18" s="52">
+      <c r="N18" s="52" t="n"/>
+      <c r="O18" s="53">
         <f>IF(J18="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J18))</f>
         <v/>
       </c>
-      <c r="P18" s="52">
+      <c r="P18" s="53">
         <f>IF(J18="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J18))</f>
         <v/>
       </c>
-      <c r="Q18" s="52">
+      <c r="Q18" s="53">
         <f>IF(J18="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J18))</f>
         <v/>
       </c>
-      <c r="R18" s="52">
+      <c r="R18" s="53">
         <f>IF(B18="","",L18*O18+M18*P18+N18*Q18)</f>
         <v/>
       </c>
-      <c r="S18" s="53" t="n">
+      <c r="S18" s="44" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="T18" s="52">
+      <c r="T18" s="53">
         <f>IF(B18="","",SUMIFS(套件单价!G:G,套件单价!A:A,B18,套件单价!B:B,K18))</f>
         <v/>
       </c>
-      <c r="U18" s="44" t="n">
+      <c r="U18" s="51" t="n">
         <v>2.5</v>
       </c>
-      <c r="V18" s="52">
+      <c r="V18" s="53">
         <f>IF(B18="","",R18+S18+T18)</f>
         <v/>
       </c>
-      <c r="W18" s="52">
+      <c r="W18" s="53">
         <f>IF(B18="","",V18+U18)</f>
         <v/>
       </c>
@@ -3952,7 +4024,7 @@
           <t>P25</t>
         </is>
       </c>
-      <c r="B19" s="44" t="n">
+      <c r="B19" s="51" t="n">
         <v>25</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3997,43 +4069,43 @@
       <c r="L19" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="M19" s="51" t="n">
+      <c r="M19" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="N19" s="51" t="n">
+      <c r="N19" s="52" t="n">
         <v>64</v>
       </c>
-      <c r="O19" s="52">
+      <c r="O19" s="53">
         <f>IF(J19="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J19))</f>
         <v/>
       </c>
-      <c r="P19" s="52">
+      <c r="P19" s="53">
         <f>IF(J19="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J19))</f>
         <v/>
       </c>
-      <c r="Q19" s="52">
+      <c r="Q19" s="53">
         <f>IF(J19="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J19))</f>
         <v/>
       </c>
-      <c r="R19" s="52">
+      <c r="R19" s="53">
         <f>IF(B19="","",L19*O19+M19*P19+N19*Q19)</f>
         <v/>
       </c>
-      <c r="S19" s="53" t="n">
+      <c r="S19" s="44" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="T19" s="52">
+      <c r="T19" s="53">
         <f>IF(B19="","",SUMIFS(套件单价!G:G,套件单价!A:A,B19,套件单价!B:B,K19))</f>
         <v/>
       </c>
-      <c r="U19" s="44" t="n">
+      <c r="U19" s="51" t="n">
         <v>2.5</v>
       </c>
-      <c r="V19" s="52">
+      <c r="V19" s="53">
         <f>IF(B19="","",R19+S19+T19)</f>
         <v/>
       </c>
-      <c r="W19" s="52">
+      <c r="W19" s="53">
         <f>IF(B19="","",V19+U19)</f>
         <v/>
       </c>
@@ -4050,7 +4122,7 @@
           <t>P20</t>
         </is>
       </c>
-      <c r="B20" s="44" t="n">
+      <c r="B20" s="51" t="n">
         <v>20</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4095,41 +4167,41 @@
       <c r="L20" s="2" t="n">
         <v>256</v>
       </c>
-      <c r="M20" s="51" t="n">
+      <c r="M20" s="52" t="n">
         <v>128</v>
       </c>
-      <c r="N20" s="51" t="n"/>
-      <c r="O20" s="52">
+      <c r="N20" s="52" t="n"/>
+      <c r="O20" s="53">
         <f>IF(J20="","",SUMIFS(灯珠单价!B:B,灯珠单价!A:A,J20))</f>
         <v/>
       </c>
-      <c r="P20" s="52">
+      <c r="P20" s="53">
         <f>IF(J20="","",SUMIFS(灯珠单价!C:C,灯珠单价!A:A,J20))</f>
         <v/>
       </c>
-      <c r="Q20" s="52">
+      <c r="Q20" s="53">
         <f>IF(J20="","",SUMIFS(灯珠单价!D:D,灯珠单价!A:A,J20))</f>
         <v/>
       </c>
-      <c r="R20" s="52">
+      <c r="R20" s="53">
         <f>IF(B20="","",L20*O20+M20*P20+N20*Q20)</f>
         <v/>
       </c>
-      <c r="S20" s="53" t="n">
+      <c r="S20" s="44" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="T20" s="52">
+      <c r="T20" s="53">
         <f>IF(B20="","",SUMIFS(套件单价!G:G,套件单价!A:A,B20,套件单价!B:B,K20))</f>
         <v/>
       </c>
-      <c r="U20" s="44" t="n">
+      <c r="U20" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="52">
+      <c r="V20" s="53">
         <f>IF(B20="","",R20+S20+T20)</f>
         <v/>
       </c>
-      <c r="W20" s="52">
+      <c r="W20" s="53">
         <f>IF(B20="","",V20+U20)</f>
         <v/>
       </c>
@@ -12875,7 +12947,7 @@
           <t>悬臂式</t>
         </is>
       </c>
-      <c r="B5" s="53" t="n">
+      <c r="B5" s="44" t="n">
         <v>25</v>
       </c>
       <c r="C5" s="61" t="n">
@@ -12963,7 +13035,7 @@
           <t>门架式</t>
         </is>
       </c>
-      <c r="B6" s="53" t="n">
+      <c r="B6" s="44" t="n">
         <v>31.25</v>
       </c>
       <c r="C6" s="61" t="n">
@@ -13047,7 +13119,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
-      <c r="B7" s="48" t="n"/>
+      <c r="B7" s="49" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="7" t="n"/>
@@ -13063,11 +13135,11 @@
       <c r="O7" s="7" t="n"/>
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="50">
+      <c r="R7" s="48">
         <f>IF(C7="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C7,模组价格!D:D,F7,模组价格!H:H,D7,模组价格!I:I,E7,模组价格!K:K,H7,模组价格!L:L,I7))</f>
         <v/>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="48">
         <f>IF(K7="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K7))</f>
         <v/>
       </c>
@@ -13075,7 +13147,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
-      <c r="B8" s="48" t="n"/>
+      <c r="B8" s="49" t="n"/>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -13091,11 +13163,11 @@
       <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="50">
+      <c r="R8" s="48">
         <f>IF(C8="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C8,模组价格!D:D,F8,模组价格!H:H,D8,模组价格!I:I,E8,模组价格!K:K,H8,模组价格!L:L,I8))</f>
         <v/>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="48">
         <f>IF(K8="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K8))</f>
         <v/>
       </c>
@@ -13103,7 +13175,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
-      <c r="B9" s="48" t="n"/>
+      <c r="B9" s="49" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="7" t="n"/>
@@ -13119,11 +13191,11 @@
       <c r="O9" s="7" t="n"/>
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="n"/>
-      <c r="R9" s="50">
+      <c r="R9" s="48">
         <f>IF(C9="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C9,模组价格!D:D,F9,模组价格!H:H,D9,模组价格!I:I,E9,模组价格!K:K,H9,模组价格!L:L,I9))</f>
         <v/>
       </c>
-      <c r="S9" s="50">
+      <c r="S9" s="48">
         <f>IF(K9="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K9))</f>
         <v/>
       </c>
@@ -13131,7 +13203,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="48" t="n"/>
+      <c r="B10" s="49" t="n"/>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="7" t="n"/>
@@ -13147,11 +13219,11 @@
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="n"/>
-      <c r="R10" s="50">
+      <c r="R10" s="48">
         <f>IF(C10="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C10,模组价格!D:D,F10,模组价格!H:H,D10,模组价格!I:I,E10,模组价格!K:K,H10,模组价格!L:L,I10))</f>
         <v/>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="48">
         <f>IF(K10="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K10))</f>
         <v/>
       </c>
@@ -13159,7 +13231,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
-      <c r="B11" s="48" t="n"/>
+      <c r="B11" s="49" t="n"/>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -13175,11 +13247,11 @@
       <c r="O11" s="7" t="n"/>
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="50">
+      <c r="R11" s="48">
         <f>IF(C11="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C11,模组价格!D:D,F11,模组价格!H:H,D11,模组价格!I:I,E11,模组价格!K:K,H11,模组价格!L:L,I11))</f>
         <v/>
       </c>
-      <c r="S11" s="50">
+      <c r="S11" s="48">
         <f>IF(K11="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K11))</f>
         <v/>
       </c>
@@ -13187,7 +13259,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
-      <c r="B12" s="48" t="n"/>
+      <c r="B12" s="49" t="n"/>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="7" t="n"/>
@@ -13203,11 +13275,11 @@
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="n"/>
-      <c r="R12" s="50">
+      <c r="R12" s="48">
         <f>IF(C12="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C12,模组价格!D:D,F12,模组价格!H:H,D12,模组价格!I:I,E12,模组价格!K:K,H12,模组价格!L:L,I12))</f>
         <v/>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="48">
         <f>IF(K12="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K12))</f>
         <v/>
       </c>
@@ -13215,7 +13287,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
-      <c r="B13" s="48" t="n"/>
+      <c r="B13" s="49" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="7" t="n"/>
@@ -13231,11 +13303,11 @@
       <c r="O13" s="7" t="n"/>
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="n"/>
-      <c r="R13" s="50">
+      <c r="R13" s="48">
         <f>IF(C13="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C13,模组价格!D:D,F13,模组价格!H:H,D13,模组价格!I:I,E13,模组价格!K:K,H13,模组价格!L:L,I13))</f>
         <v/>
       </c>
-      <c r="S13" s="50">
+      <c r="S13" s="48">
         <f>IF(K13="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K13))</f>
         <v/>
       </c>
@@ -13243,7 +13315,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
-      <c r="B14" s="48" t="n"/>
+      <c r="B14" s="49" t="n"/>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="7" t="n"/>
@@ -13259,11 +13331,11 @@
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="50">
+      <c r="R14" s="48">
         <f>IF(C14="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C14,模组价格!D:D,F14,模组价格!H:H,D14,模组价格!I:I,E14,模组价格!K:K,H14,模组价格!L:L,I14))</f>
         <v/>
       </c>
-      <c r="S14" s="50">
+      <c r="S14" s="48">
         <f>IF(K14="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K14))</f>
         <v/>
       </c>
@@ -13271,7 +13343,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
-      <c r="B15" s="48" t="n"/>
+      <c r="B15" s="49" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="7" t="n"/>
@@ -13287,11 +13359,11 @@
       <c r="O15" s="7" t="n"/>
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="n"/>
-      <c r="R15" s="50">
+      <c r="R15" s="48">
         <f>IF(C15="","",SUMIFS(模组价格!X:X,模组价格!A:A,"是",模组价格!C:C,C15,模组价格!D:D,F15,模组价格!H:H,D15,模组价格!I:I,E15,模组价格!K:K,H15,模组价格!L:L,I15))</f>
         <v/>
       </c>
-      <c r="S15" s="50">
+      <c r="S15" s="48">
         <f>IF(K15="","",SUMIFS(箱体单价!J:J,箱体单价!A:A,"是",箱体单价!C:C,K15))</f>
         <v/>
       </c>
